--- a/E/IFD04D.xlsx
+++ b/E/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="363">
   <si>
     <t/>
   </si>
@@ -202,6 +202,432 @@
     <t>SEDAAP MIE STO.MDR82</t>
   </si>
   <si>
+    <t>20132986</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI TRYKI120</t>
+  </si>
+  <si>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
+  </si>
+  <si>
+    <t>20140633</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG SPC 5S</t>
+  </si>
+  <si>
+    <t>20140657</t>
+  </si>
+  <si>
+    <t>INDOMIE AYAM BWG 5S</t>
+  </si>
+  <si>
+    <t>20143284</t>
+  </si>
+  <si>
+    <t>WOWSPAGETIGORENG79G</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI CARB80</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGHETI BOLOG76</t>
+  </si>
+  <si>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW AGLI OLIO 75G</t>
+  </si>
+  <si>
+    <t>20138738</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI CRBO 80G</t>
+  </si>
+  <si>
+    <t>20138739</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI BGLN 84G</t>
+  </si>
+  <si>
+    <t>20143393</t>
+  </si>
+  <si>
+    <t>I/P SPGT FR CKN CB80</t>
+  </si>
+  <si>
+    <t>20143392</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI PZA BL80</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10003435</t>
+  </si>
+  <si>
+    <t>SUPERMI AYAM BWG 75G</t>
+  </si>
+  <si>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
+  </si>
+  <si>
+    <t>20085444</t>
+  </si>
+  <si>
+    <t>GAGA 100 GR.JLPNO 85</t>
+  </si>
+  <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG CB.IJO85</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
+  </si>
+  <si>
+    <t>20128381</t>
+  </si>
+  <si>
+    <t>INDOMI TRI MSO RMN86</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20132338</t>
+  </si>
+  <si>
+    <t>INDOMIE TORI KARA 89</t>
+  </si>
+  <si>
+    <t>20135989</t>
+  </si>
+  <si>
+    <t>INDOMI SPCY RMYEON83</t>
+  </si>
+  <si>
+    <t>20135990</t>
+  </si>
+  <si>
+    <t>INDOMI FIERY CHKIN94</t>
+  </si>
+  <si>
+    <t>20136533</t>
+  </si>
+  <si>
+    <t>INDOMIE K-ROSE 85G</t>
+  </si>
+  <si>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMIE GR AYM.GP 85</t>
+  </si>
+  <si>
+    <t>20032100</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/AYM PG90</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20032099</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/GR.SPC90</t>
+  </si>
+  <si>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>20142599</t>
+  </si>
+  <si>
+    <t>INDOMI GR CB.IJO 120</t>
+  </si>
+  <si>
+    <t>20085013</t>
+  </si>
+  <si>
+    <t>BD MIE URAI ORG 140G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10000507</t>
+  </si>
+  <si>
+    <t>A/B MIE TELOR 200GR</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004055</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR MRH200</t>
+  </si>
+  <si>
+    <t>10004262</t>
+  </si>
+  <si>
+    <t>3AYAM MIE TLR KNG200</t>
+  </si>
+  <si>
+    <t>10037027</t>
+  </si>
+  <si>
+    <t>AAA BIHUN 220GR</t>
+  </si>
+  <si>
+    <t>20043409</t>
+  </si>
+  <si>
+    <t>IDM BIHUN BERAS 220G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20034699</t>
+  </si>
+  <si>
+    <t>BIHUN JAGUNG 320G</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>10000245</t>
+  </si>
+  <si>
+    <t>RATU ABON SAPI 90G</t>
+  </si>
+  <si>
+    <t>20140909</t>
+  </si>
+  <si>
+    <t>B.FARM TERI KB 60G</t>
+  </si>
+  <si>
+    <t>20020770</t>
+  </si>
+  <si>
+    <t>MERBABU KR.BAWANG200</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20112822</t>
+  </si>
+  <si>
+    <t>MIGELAS AYAM BWG 6'S</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20094642</t>
+  </si>
+  <si>
+    <t>MIGELAS SOTO AYAM 6S</t>
+  </si>
+  <si>
+    <t>20032996</t>
+  </si>
+  <si>
+    <t>PALDO HOT&amp;SPICY 120</t>
+  </si>
+  <si>
+    <t>20138114</t>
+  </si>
+  <si>
+    <t>PALDO BIBMEN II 130G</t>
+  </si>
+  <si>
     <t>20099679</t>
   </si>
   <si>
@@ -214,420 +640,6 @@
     <t>LEMONILO PDS KOREA68</t>
   </si>
   <si>
-    <t>20132986</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI TRYKI120</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
-  </si>
-  <si>
-    <t>20143284</t>
-  </si>
-  <si>
-    <t>WOWSPAGETIGORENG79G</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI CARB80</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGHETI BOLOG76</t>
-  </si>
-  <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW AGLI OLIO 75G</t>
-  </si>
-  <si>
-    <t>20138738</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI CRBO 80G</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10003435</t>
-  </si>
-  <si>
-    <t>SUPERMI AYAM BWG 75G</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
-  </si>
-  <si>
-    <t>20085444</t>
-  </si>
-  <si>
-    <t>GAGA 100 GR.JLPNO 85</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG CB.IJO85</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>20128381</t>
-  </si>
-  <si>
-    <t>INDOMI TRI MSO RMN86</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20132338</t>
-  </si>
-  <si>
-    <t>INDOMIE TORI KARA 89</t>
-  </si>
-  <si>
-    <t>20135989</t>
-  </si>
-  <si>
-    <t>INDOMI SPCY RMYEON83</t>
-  </si>
-  <si>
-    <t>20135990</t>
-  </si>
-  <si>
-    <t>INDOMI FIERY CHKIN94</t>
-  </si>
-  <si>
-    <t>20136533</t>
-  </si>
-  <si>
-    <t>INDOMIE K-ROSE 85G</t>
-  </si>
-  <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMIE GR AYM.GP 85</t>
-  </si>
-  <si>
-    <t>20032100</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/AYM PG90</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20032099</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/GR.SPC90</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>20142599</t>
-  </si>
-  <si>
-    <t>INDOMI GR CB.IJO 120</t>
-  </si>
-  <si>
-    <t>20085013</t>
-  </si>
-  <si>
-    <t>BD MIE URAI ORG 140G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10000507</t>
-  </si>
-  <si>
-    <t>A/B MIE TELOR 200GR</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004055</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR MRH200</t>
-  </si>
-  <si>
-    <t>10004262</t>
-  </si>
-  <si>
-    <t>3AYAM MIE TLR KNG200</t>
-  </si>
-  <si>
-    <t>10037027</t>
-  </si>
-  <si>
-    <t>AAA BIHUN 220GR</t>
-  </si>
-  <si>
-    <t>20043409</t>
-  </si>
-  <si>
-    <t>IDM BIHUN BERAS 220G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20034699</t>
-  </si>
-  <si>
-    <t>BIHUN JAGUNG 320G</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>10000245</t>
-  </si>
-  <si>
-    <t>RATU ABON SAPI 90G</t>
-  </si>
-  <si>
-    <t>20140909</t>
-  </si>
-  <si>
-    <t>B.FARM TERI KB 60G</t>
-  </si>
-  <si>
-    <t>20020770</t>
-  </si>
-  <si>
-    <t>MERBABU KR.BAWANG200</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20112822</t>
-  </si>
-  <si>
-    <t>MIGELAS AYAM BWG 6'S</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20094642</t>
-  </si>
-  <si>
-    <t>MIGELAS SOTO AYAM 6S</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
-  </si>
-  <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
-  </si>
-  <si>
     <t>20127764</t>
   </si>
   <si>
@@ -877,16 +889,16 @@
     <t>SEDAAP MIE K/S CUP81</t>
   </si>
   <si>
+    <t>20130519</t>
+  </si>
+  <si>
+    <t>SDP MI AYM NMPOL 75G</t>
+  </si>
+  <si>
     <t>20113844</t>
   </si>
   <si>
     <t>SEDAAP MI AYM JRT 75</t>
-  </si>
-  <si>
-    <t>20130519</t>
-  </si>
-  <si>
-    <t>SDP MI AYM NMPOL 75G</t>
   </si>
   <si>
     <t>20122255</t>
@@ -1480,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2065,7 +2077,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>19</v>
@@ -2085,7 +2097,7 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -2105,10 +2117,10 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2125,10 +2137,10 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3322,10 +3334,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3333,19 +3345,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3353,19 +3365,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>19</v>
@@ -3382,10 +3394,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>19</v>
@@ -3402,13 +3414,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,13 +3434,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,13 +3454,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,30 +3474,30 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3493,19 +3505,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>222</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3522,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3542,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>19</v>
@@ -3553,19 +3565,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>19</v>
@@ -3573,22 +3585,22 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3602,13 +3614,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,13 +3634,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3642,13 +3654,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3662,10 +3674,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3673,19 +3685,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3693,19 +3705,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3722,10 +3734,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3742,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3762,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3782,10 +3794,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3802,10 +3814,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3813,19 +3825,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3833,19 +3845,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3862,10 +3874,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
@@ -3882,13 +3894,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,53 +3914,53 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3962,13 +3974,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3982,13 +3994,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4002,13 +4014,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4022,10 +4034,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4042,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4053,19 +4065,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4073,19 +4085,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="E130" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4102,10 +4114,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4122,10 +4134,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -4142,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>19</v>
@@ -4162,13 +4174,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,13 +4194,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,10 +4214,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>171</v>
@@ -4222,50 +4234,50 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>19</v>
@@ -4282,10 +4294,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>19</v>
@@ -4302,50 +4314,50 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4362,10 +4374,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4382,10 +4394,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4402,10 +4414,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4422,10 +4434,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4442,10 +4454,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4453,19 +4465,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4473,19 +4485,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4502,10 +4514,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4522,10 +4534,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4542,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4553,19 +4565,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4573,19 +4585,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4602,10 +4614,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -4622,53 +4634,53 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4682,10 +4694,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>186</v>
@@ -4702,13 +4714,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,12 +4734,52 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="F164" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/E/IFD04D.xlsx
+++ b/E/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
   <si>
     <t/>
   </si>
@@ -220,18 +220,6 @@
     <t>TASTY BAKMI YKNKU115</t>
   </si>
   <si>
-    <t>20140633</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG SPC 5S</t>
-  </si>
-  <si>
-    <t>20140657</t>
-  </si>
-  <si>
-    <t>INDOMIE AYAM BWG 5S</t>
-  </si>
-  <si>
     <t>20143284</t>
   </si>
   <si>
@@ -614,18 +602,6 @@
   </si>
   <si>
     <t>MIGELAS SOTO AYAM 6S</t>
-  </si>
-  <si>
-    <t>20032996</t>
-  </si>
-  <si>
-    <t>PALDO HOT&amp;SPICY 120</t>
-  </si>
-  <si>
-    <t>20138114</t>
-  </si>
-  <si>
-    <t>PALDO BIBMEN II 130G</t>
   </si>
   <si>
     <t>20099679</t>
@@ -1492,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F164"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2114,13 +2090,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2134,13 +2110,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2157,7 +2133,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2177,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -2197,10 +2173,10 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2217,10 +2193,10 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2237,7 +2213,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2257,7 +2233,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2265,19 +2241,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2285,19 +2261,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2314,10 +2290,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2334,10 +2310,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2354,10 +2330,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2365,19 +2341,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2385,19 +2361,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2414,10 +2390,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2434,10 +2410,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2454,10 +2430,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2465,19 +2441,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2485,19 +2461,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2514,10 +2490,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2534,10 +2510,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2554,10 +2530,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2565,19 +2541,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2585,19 +2561,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2614,10 +2590,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2634,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2654,10 +2630,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2674,10 +2650,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2685,19 +2661,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2705,16 +2681,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>4</v>
@@ -2725,16 +2701,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>18</v>
@@ -2745,19 +2721,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2774,10 +2750,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2794,10 +2770,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2814,10 +2790,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2834,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2854,10 +2830,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2865,19 +2841,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2885,19 +2861,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2914,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2934,10 +2910,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2954,10 +2930,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -2974,73 +2950,73 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3054,13 +3030,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3074,93 +3050,93 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>171</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="E82" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3174,13 +3150,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3194,30 +3170,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>19</v>
@@ -3225,39 +3201,39 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>195</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
@@ -3274,13 +3250,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3294,50 +3270,50 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3345,19 +3321,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
@@ -3365,22 +3341,22 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3394,13 +3370,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3414,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>19</v>
@@ -3434,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3445,59 +3421,59 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3505,19 +3481,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3525,19 +3501,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3545,59 +3521,59 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>19</v>
@@ -3614,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
@@ -3634,50 +3610,50 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3685,19 +3661,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3705,19 +3681,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3734,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3754,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3774,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3785,19 +3761,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3805,19 +3781,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3825,19 +3801,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3845,22 +3821,22 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3874,70 +3850,70 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3945,22 +3921,22 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,13 +3950,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,13 +3970,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4014,30 +3990,30 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4045,19 +4021,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4065,19 +4041,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4085,19 +4061,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4114,10 +4090,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4134,13 +4110,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4154,13 +4130,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4174,13 +4150,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4194,10 +4170,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>19</v>
@@ -4205,159 +4181,159 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>171</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4374,10 +4350,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4394,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4414,10 +4390,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4425,19 +4401,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4445,19 +4421,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4465,19 +4441,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4485,19 +4461,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4514,10 +4490,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4525,19 +4501,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4545,19 +4521,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4565,19 +4541,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4585,99 +4561,99 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>19</v>
@@ -4694,92 +4670,12 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F164" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/E/IFD04D.xlsx
+++ b/E/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="360">
   <si>
     <t/>
   </si>
@@ -661,15 +661,27 @@
     <t>WONHAE TPOKI CARB 80</t>
   </si>
   <si>
+    <t>20135130</t>
+  </si>
+  <si>
+    <t>NISSIN SLTD.EGG 117G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20135131</t>
+  </si>
+  <si>
+    <t>NISSIN SPC S.EGG 117</t>
+  </si>
+  <si>
     <t>20019479</t>
   </si>
   <si>
     <t>N/SHIM SPCY MUSHR120</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>20115156</t>
   </si>
   <si>
@@ -682,72 +694,60 @@
     <t>MJGAE SPCY RPKI 155G</t>
   </si>
   <si>
+    <t>20096499</t>
+  </si>
+  <si>
+    <t>SMYANG AYM CRBO 130G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20052583</t>
+  </si>
+  <si>
+    <t>SMYANG GR PDS AYM140</t>
+  </si>
+  <si>
+    <t>20127820</t>
+  </si>
+  <si>
+    <t>SMYANG CRM CBNARA140</t>
+  </si>
+  <si>
+    <t>20112749</t>
+  </si>
+  <si>
+    <t>SAMYANG SPICY 120G</t>
+  </si>
+  <si>
+    <t>20138572</t>
+  </si>
+  <si>
+    <t>SAMYANG ROSE 140G</t>
+  </si>
+  <si>
+    <t>20139702</t>
+  </si>
+  <si>
+    <t>SMYANG QTR.CHSE 145G</t>
+  </si>
+  <si>
     <t>20117989</t>
   </si>
   <si>
     <t>M/S TOPOKKI ORI 132G</t>
   </si>
   <si>
-    <t>20096499</t>
-  </si>
-  <si>
-    <t>SMYANG AYM CRBO 130G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20052583</t>
-  </si>
-  <si>
-    <t>SMYANG GR PDS AYM140</t>
-  </si>
-  <si>
-    <t>20127820</t>
-  </si>
-  <si>
-    <t>SMYANG CRM CBNARA140</t>
-  </si>
-  <si>
-    <t>20112749</t>
-  </si>
-  <si>
-    <t>SAMYANG SPICY 120G</t>
-  </si>
-  <si>
-    <t>20138572</t>
-  </si>
-  <si>
-    <t>SAMYANG ROSE 140G</t>
-  </si>
-  <si>
-    <t>20139702</t>
-  </si>
-  <si>
-    <t>SMYANG QTR.CHSE 145G</t>
-  </si>
-  <si>
-    <t>20135130</t>
-  </si>
-  <si>
-    <t>NISSIN SLTD.EGG 117G</t>
+    <t>20031775</t>
+  </si>
+  <si>
+    <t>NISSIN GEKIKARA 109G</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>20135131</t>
-  </si>
-  <si>
-    <t>NISSIN SPC S.EGG 117</t>
-  </si>
-  <si>
-    <t>20031775</t>
-  </si>
-  <si>
-    <t>NISSIN GEKIKARA 109G</t>
-  </si>
-  <si>
     <t>20067395</t>
   </si>
   <si>
@@ -770,6 +770,21 @@
   </si>
   <si>
     <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>20143800</t>
+  </si>
+  <si>
+    <t>CNCMN C/RMN KJ PDS75</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20143801</t>
+  </si>
+  <si>
+    <t>CNCMN C/RMN EX PDS75</t>
   </si>
   <si>
     <t>20039494</t>
@@ -1468,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3413,7 +3428,7 @@
         <v>218</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3433,7 +3448,7 @@
         <v>218</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3453,7 +3468,7 @@
         <v>218</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3473,7 +3488,7 @@
         <v>218</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3490,10 +3505,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3501,19 +3516,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3530,13 +3545,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3550,10 +3565,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3570,13 +3585,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3590,10 +3605,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
@@ -3610,10 +3625,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3621,19 +3636,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3641,19 +3656,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3670,10 +3685,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3690,10 +3705,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3710,10 +3725,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3730,10 +3745,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3750,13 +3765,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3770,13 +3785,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3790,10 +3805,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3801,19 +3816,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3821,42 +3836,42 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,13 +3885,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3890,90 +3905,90 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>19</v>
@@ -3981,19 +3996,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4010,10 +4025,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4030,10 +4045,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4041,19 +4056,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4061,19 +4076,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4081,19 +4096,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4101,59 +4116,59 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>167</v>
@@ -4161,22 +4176,22 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4190,13 +4205,13 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4210,10 +4225,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4221,19 +4236,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4241,22 +4256,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4270,13 +4285,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4290,10 +4305,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4301,19 +4316,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4321,19 +4336,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4341,19 +4356,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4361,19 +4376,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4381,19 +4396,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4410,10 +4425,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4430,10 +4445,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4441,19 +4456,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4461,19 +4476,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4481,19 +4496,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4510,10 +4525,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4530,10 +4545,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4541,19 +4556,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4561,22 +4576,22 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4590,13 +4605,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4610,30 +4625,30 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>182</v>
@@ -4641,41 +4656,81 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F160" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>19</v>
       </c>
     </row>
